--- a/testdata/Outlet.xlsx
+++ b/testdata/Outlet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\stp-automation-test\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF8075A-2A07-4856-B610-271C85B05B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F9CE87-30D6-4C02-887E-64550221C571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C7681F3F-D0BE-43DE-AC81-0EAE175E5E0E}"/>
   </bookViews>
@@ -127,7 +127,7 @@
     <t>Pondok indah mall 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Cabang Pondok Indah </t>
+    <t>Cabang Pondok Indah</t>
   </si>
 </sst>
 </file>

--- a/testdata/Outlet.xlsx
+++ b/testdata/Outlet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\stp-automation-test\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\sales-force-automation-test\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F9CE87-30D6-4C02-887E-64550221C571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A74368-CCB0-4ADD-8042-5C84E8B462EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C7681F3F-D0BE-43DE-AC81-0EAE175E5E0E}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
   <si>
     <t>customerName</t>
   </si>
@@ -128,6 +128,33 @@
   </si>
   <si>
     <t>Cabang Pondok Indah</t>
+  </si>
+  <si>
+    <t>longtitudeLatitude</t>
+  </si>
+  <si>
+    <t>-6.1648863244805625, 106.76346571069685</t>
+  </si>
+  <si>
+    <t>-6.217946979432403, 106.77798395302567</t>
+  </si>
+  <si>
+    <t>-6.238259352967404, 106.78330598371257</t>
+  </si>
+  <si>
+    <t>-6.264992633784614, 106.78439159720519</t>
+  </si>
+  <si>
+    <t>Komp. Ruko Green Garden Blk. Z, Jl. Panjang Arteri Klp. Dua Raya No.5 4 No.15, RT.5/RW.8, Kedoya Utara, Kec. Kb. Jeruk, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11520</t>
+  </si>
+  <si>
+    <t>Jl. Raya Kby. Lama No.64, RT.6/RW.8, Sukabumi Sel., Kec. Kb. Jeruk, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11560</t>
+  </si>
+  <si>
+    <t>Jl. Sultan Iskandar Muda No.7, RT.8/RW.1, Kby. Lama Utara, Kec. Kby. Lama, Kota Jakarta Selatan, Daerah Khusus Ibukota Jakarta 12220</t>
+  </si>
+  <si>
+    <t>Jl. Metro Pondok Indah No.Kav. 4, RT.1/RW.16, Pd. Pinang, Kec. Kby. Lama, Kota Jakarta Selatan, Daerah Khusus Ibukota Jakarta 12310</t>
   </si>
 </sst>
 </file>
@@ -500,17 +527,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7337974C-AECA-4E71-AAF1-A86156BF7000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.6640625" customWidth="1"/>
+    <col min="7" max="7" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -527,19 +556,22 @@
         <v>8</v>
       </c>
       <c r="F1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -552,20 +584,26 @@
       <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -578,20 +616,26 @@
       <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -604,20 +648,26 @@
       <c r="D4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
         <v>23</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -630,16 +680,22 @@
       <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>4</v>
       </c>
     </row>
